--- a/6.4 Bonaire with disturbances/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/6.4 Bonaire with disturbances/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.986081496192724</v>
+        <v>2.04969078759659</v>
       </c>
       <c r="C3" t="n">
-        <v>2.878298189938415</v>
+        <v>2.956390787828934</v>
       </c>
       <c r="D3" t="n">
-        <v>37.10489922760509</v>
+        <v>38.18020109347724</v>
       </c>
       <c r="E3" t="n">
-        <v>41.96927891373623</v>
+        <v>43.18628266890276</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.91695074983528</v>
+        <v>2.026187877379069</v>
       </c>
       <c r="C4" t="n">
-        <v>2.947353870304561</v>
+        <v>3.068519918936959</v>
       </c>
       <c r="D4" t="n">
-        <v>36.80163736176326</v>
+        <v>38.89199372372271</v>
       </c>
       <c r="E4" t="n">
-        <v>41.6659419819031</v>
+        <v>43.98670152003874</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.8930059233287</v>
+        <v>2.016048932476596</v>
       </c>
       <c r="C5" t="n">
-        <v>3.056445675200467</v>
+        <v>3.206184149315583</v>
       </c>
       <c r="D5" t="n">
-        <v>36.22443843400542</v>
+        <v>39.24016655939445</v>
       </c>
       <c r="E5" t="n">
-        <v>41.17389003253459</v>
+        <v>44.46239964118662</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853961817130804</v>
+        <v>2.003317594531</v>
       </c>
       <c r="C6" t="n">
-        <v>3.280814295529034</v>
+        <v>3.437785725447791</v>
       </c>
       <c r="D6" t="n">
-        <v>36.40138864021888</v>
+        <v>40.2768738733262</v>
       </c>
       <c r="E6" t="n">
-        <v>41.53616475287871</v>
+        <v>45.71797719330499</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9059076940937443</v>
+        <v>0.9583705553096977</v>
       </c>
       <c r="C7" t="n">
-        <v>2.264273452643716</v>
+        <v>2.305204953490075</v>
       </c>
       <c r="D7" t="n">
-        <v>26.70171150478334</v>
+        <v>29.85827364073916</v>
       </c>
       <c r="E7" t="n">
-        <v>29.8718926515208</v>
+        <v>33.12184914953893</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9657943040527999</v>
+        <v>1.018435655688976</v>
       </c>
       <c r="C8" t="n">
-        <v>2.742816553601782</v>
+        <v>2.720545785736022</v>
       </c>
       <c r="D8" t="n">
-        <v>27.5152465573845</v>
+        <v>31.20926748153785</v>
       </c>
       <c r="E8" t="n">
-        <v>31.22385741503908</v>
+        <v>34.94824892296285</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.631764465159865</v>
+        <v>0.6779949645528472</v>
       </c>
       <c r="C9" t="n">
-        <v>2.374778974233737</v>
+        <v>2.317778702525167</v>
       </c>
       <c r="D9" t="n">
-        <v>22.44117190527825</v>
+        <v>25.68371767529574</v>
       </c>
       <c r="E9" t="n">
-        <v>25.44771534467185</v>
+        <v>28.67949134237375</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5996809501850792</v>
+        <v>0.6320295370400115</v>
       </c>
       <c r="C10" t="n">
-        <v>2.756541386507152</v>
+        <v>2.592373535403</v>
       </c>
       <c r="D10" t="n">
-        <v>21.41440125131468</v>
+        <v>24.41167699238019</v>
       </c>
       <c r="E10" t="n">
-        <v>24.77062358800691</v>
+        <v>27.6360800648232</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6530978427731482</v>
+        <v>0.6721339307584938</v>
       </c>
       <c r="C11" t="n">
-        <v>3.562674061418293</v>
+        <v>3.262416343551448</v>
       </c>
       <c r="D11" t="n">
-        <v>22.2736072071174</v>
+        <v>25.46806697458089</v>
       </c>
       <c r="E11" t="n">
-        <v>26.48937911130884</v>
+        <v>29.40261724889083</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7201708459272902</v>
+        <v>0.7296348937962295</v>
       </c>
       <c r="C12" t="n">
-        <v>4.644726928608</v>
+        <v>4.156111096204363</v>
       </c>
       <c r="D12" t="n">
-        <v>23.22478328785397</v>
+        <v>26.73274454971458</v>
       </c>
       <c r="E12" t="n">
-        <v>28.58968106238926</v>
+        <v>31.61849053971518</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7811962832232719</v>
+        <v>0.7944007898453916</v>
       </c>
       <c r="C13" t="n">
-        <v>5.928450409204086</v>
+        <v>5.210576852904734</v>
       </c>
       <c r="D13" t="n">
-        <v>24.92067390712399</v>
+        <v>28.80578336704806</v>
       </c>
       <c r="E13" t="n">
-        <v>31.63032059955135</v>
+        <v>34.81076100979819</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8286441497695203</v>
+        <v>0.8444895577160638</v>
       </c>
       <c r="C14" t="n">
-        <v>7.41614179283449</v>
+        <v>6.421641185909515</v>
       </c>
       <c r="D14" t="n">
-        <v>26.10856899430855</v>
+        <v>30.40476567043189</v>
       </c>
       <c r="E14" t="n">
-        <v>34.35335493691256</v>
+        <v>37.67089641405747</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8655774984032852</v>
+        <v>0.8784874807141309</v>
       </c>
       <c r="C15" t="n">
-        <v>9.06364206776219</v>
+        <v>7.739873098309877</v>
       </c>
       <c r="D15" t="n">
-        <v>27.8467238522464</v>
+        <v>32.65773920699972</v>
       </c>
       <c r="E15" t="n">
-        <v>37.77594341841188</v>
+        <v>41.27609978602373</v>
       </c>
     </row>
   </sheetData>
